--- a/src/modules/excel/__tests__/data/gold-standard.xlsx
+++ b/src/modules/excel/__tests__/data/gold-standard.xlsx
@@ -54,7 +54,7 @@
     <t>Hyperlink</t>
   </si>
   <si>
-    <t>excelts</t>
+    <t>documonster</t>
   </si>
 </sst>
 </file>
